--- a/SHOP_Qcut_約轉最後建檔日及交易日時間差.xlsx
+++ b/SHOP_Qcut_約轉最後建檔日及交易日時間差.xlsx
@@ -413,36 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>SHAP_Min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SHAP_Max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Feature_Mean</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SHAP_Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SHAP_Median</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>SHAP_Std</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Fraud_Prob</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cnt</t>
         </is>
@@ -450,201 +460,261 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>-0.5745999813079834</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.283100008964539</v>
+      </c>
+      <c r="C2" t="n">
         <v>203.8734</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>0.4887999892234802</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>0.4970999956130981</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.3657999932765961</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>0.8614000082015991</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1414</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>-0.1752000004053116</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.302000045776367</v>
+      </c>
+      <c r="C3" t="n">
         <v>388.7896</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>0.6855000257492065</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>0.7443000078201294</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.2928999960422516</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.8618999719619751</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>1407</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>-0.7214999794960022</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.091799974441528</v>
+      </c>
+      <c r="C4" t="n">
         <v>909.9922</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>0.1958000063896179</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>0.2345999926328659</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.3413999974727631</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.8694999814033508</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>1412</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>-0.8554999828338623</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.454800009727478</v>
+      </c>
+      <c r="C5" t="n">
         <v>1530.6104</v>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>0.3073999881744385</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>0.3219000101089478</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.4429999887943268</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>0.8658999800682068</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>1409</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>-0.8398000001907349</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.3607999980449677</v>
+      </c>
+      <c r="C6" t="n">
         <v>2793.0255</v>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>-0.2293000072240829</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>-0.2168000042438507</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.2337999939918518</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>0.8628000020980835</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>-1.129999995231628</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2694999873638153</v>
+      </c>
+      <c r="C7" t="n">
         <v>4141.2106</v>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>-0.4480000138282776</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>-0.488099992275238</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.256199985742569</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>0.8726999759674072</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1410</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>-0.8312000036239624</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8549000024795532</v>
+      </c>
+      <c r="C8" t="n">
         <v>6637.6388</v>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>0.3837999999523163</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>0.4990000128746033</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>0.3546999990940094</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>0.862500011920929</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>1409</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>0.01610000059008598</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.092499971389771</v>
+      </c>
+      <c r="C9" t="n">
         <v>6878.4725</v>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>0.5618000030517578</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>0.5685999989509583</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.1750999987125397</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>0.8634999990463257</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>1420</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>-0.06560000032186508</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.324100017547607</v>
+      </c>
+      <c r="C10" t="n">
         <v>7047.474</v>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>0.7075999975204468</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>0.7210999727249146</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.2353000044822693</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>0.8648999929428101</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>1405</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>-2.57039999961853</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.092399954795837</v>
+      </c>
+      <c r="C11" t="n">
         <v>7730.6835</v>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>-0.1528999954462051</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>0.1553000062704086</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>0.8535000085830688</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>0.8641999959945679</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>1406</v>
       </c>
     </row>
